--- a/output/Tables/2019/Monte Carlo/1km_value_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/1km_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.1649596130865272</v>
+        <v>0.1650542626678871</v>
       </c>
       <c r="B2">
-        <v>0.1734708176656596</v>
+        <v>0.1732964994962477</v>
       </c>
       <c r="C2">
-        <v>0.1812966908676092</v>
+        <v>0.180881081784954</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/output/Tables/2019/Monte Carlo/1km_value_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/1km_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.1650542626678871</v>
+        <v>0.1651888028097898</v>
       </c>
       <c r="B2">
-        <v>0.1732964994962477</v>
+        <v>0.1734439321830256</v>
       </c>
       <c r="C2">
-        <v>0.180881081784954</v>
+        <v>0.1810403131203978</v>
       </c>
       <c r="D2">
         <v>1</v>
